--- a/docs/FCC-core-55-70/FCC-core-PRD-v1.0-2026-06-30.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-PRD-v1.0-2026-06-30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/palakjain/Vibe_Coding/finwise/docs/FCC-core-55-70/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE75F72-C541-474F-8AFC-D98C56AD24F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AA3619-2A68-3A41-BD9F-A57F77998EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8340" yWindow="0" windowWidth="25260" windowHeight="19880" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6370" uniqueCount="2508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6371" uniqueCount="2509">
   <si>
     <t>Section</t>
   </si>
@@ -8165,6 +8165,9 @@
   </si>
   <si>
     <t>Is user providing TTM ROI on particular asset? If yes, why it say not editable?</t>
+  </si>
+  <si>
+    <t>Which kind T-bills will be? And what is HYSA?</t>
   </si>
 </sst>
 </file>
@@ -8361,6 +8364,12 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -8370,12 +8379,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9027,151 +9030,151 @@
       <c r="B14" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
     </row>
     <row r="15" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="20"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
     </row>
     <row r="16" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="20"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="22"/>
     </row>
     <row r="17" spans="2:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="20"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
     </row>
     <row r="18" spans="2:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="20"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22"/>
     </row>
     <row r="19" spans="2:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="20"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22"/>
     </row>
     <row r="20" spans="2:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="20"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22"/>
     </row>
     <row r="21" spans="2:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="20"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="22"/>
     </row>
     <row r="22" spans="2:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="20"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="22"/>
     </row>
     <row r="23" spans="2:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="20"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
     </row>
     <row r="24" spans="2:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="20"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
     </row>
     <row r="25" spans="2:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="20"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22"/>
     </row>
     <row r="26" spans="2:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="20"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
     </row>
     <row r="27" spans="2:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="20"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
     </row>
     <row r="28" spans="2:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="20"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -9253,7 +9256,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>99</v>
       </c>
@@ -9290,7 +9293,7 @@
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
     </row>
-    <row r="3" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>110</v>
       </c>
@@ -9327,7 +9330,7 @@
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
     </row>
-    <row r="4" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>121</v>
       </c>
@@ -9364,7 +9367,7 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>132</v>
       </c>
@@ -9401,7 +9404,7 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>143</v>
       </c>
@@ -9438,7 +9441,7 @@
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>154</v>
       </c>
@@ -9475,7 +9478,7 @@
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
     </row>
-    <row r="8" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>165</v>
       </c>
@@ -9512,7 +9515,7 @@
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
-    <row r="9" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>176</v>
       </c>
@@ -9549,7 +9552,7 @@
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
     </row>
-    <row r="10" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>186</v>
       </c>
@@ -9586,7 +9589,7 @@
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
     </row>
-    <row r="11" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>197</v>
       </c>
@@ -9623,7 +9626,7 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
     </row>
-    <row r="12" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>208</v>
       </c>
@@ -12091,7 +12094,7 @@
     <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="16.33203125" style="24" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" style="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -12128,7 +12131,7 @@
       <c r="K1" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="18" t="s">
         <v>2506</v>
       </c>
     </row>
@@ -12166,7 +12169,7 @@
       <c r="K2" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="L2" s="24" t="s">
+      <c r="L2" s="19" t="s">
         <v>2507</v>
       </c>
     </row>
@@ -12553,6 +12556,9 @@
       </c>
       <c r="K13" s="12" t="s">
         <v>481</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>2508</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="108" customHeight="1" x14ac:dyDescent="0.2">
@@ -29712,14 +29718,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="23" t="s">
         <v>2397</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
     </row>
     <row r="3" spans="1:6" ht="121.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
@@ -29964,7 +29970,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>2452</v>
       </c>

--- a/docs/FCC-core-55-70/FCC-core-PRD-v1.0-2026-06-30.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-PRD-v1.0-2026-06-30.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/palakjain/Vibe_Coding/finwise/docs/FCC-core-55-70/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AA3619-2A68-3A41-BD9F-A57F77998EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560A4D94-395D-5F46-A413-51641E8BDE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="0" windowWidth="25260" windowHeight="19880" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview &amp; how to read" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6371" uniqueCount="2509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6383" uniqueCount="2520">
   <si>
     <t>Section</t>
   </si>
@@ -8168,6 +8168,39 @@
   </si>
   <si>
     <t>Which kind T-bills will be? And what is HYSA?</t>
+  </si>
+  <si>
+    <t>what's this used for?</t>
+  </si>
+  <si>
+    <t>cash means cash+ cashequivalents?</t>
+  </si>
+  <si>
+    <t>why is value any versus float?</t>
+  </si>
+  <si>
+    <t>same comment as #13</t>
+  </si>
+  <si>
+    <t>we should capture as some debt might not be due for many years</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ensure to import institution name as well. </t>
+  </si>
+  <si>
+    <t>how about one time income?</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>What's the cost differential?</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -9670,16 +9703,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D171"/>
+  <dimension ref="A1:E171"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="5" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="120" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -9692,8 +9726,11 @@
       <c r="D1" s="1" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E1" s="18" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>221</v>
       </c>
@@ -9707,7 +9744,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>221</v>
       </c>
@@ -9721,7 +9758,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>221</v>
       </c>
@@ -9735,7 +9772,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>221</v>
       </c>
@@ -9749,7 +9786,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>221</v>
       </c>
@@ -9763,7 +9800,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>221</v>
       </c>
@@ -9777,7 +9814,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>221</v>
       </c>
@@ -9791,7 +9828,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>221</v>
       </c>
@@ -9804,8 +9841,11 @@
       <c r="D9" s="3" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E9" s="19" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>221</v>
       </c>
@@ -9819,7 +9859,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>221</v>
       </c>
@@ -9833,7 +9873,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>221</v>
       </c>
@@ -9847,7 +9887,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>221</v>
       </c>
@@ -9861,7 +9901,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>221</v>
       </c>
@@ -9875,7 +9915,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>221</v>
       </c>
@@ -9889,7 +9929,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>221</v>
       </c>
@@ -9903,7 +9943,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>221</v>
       </c>
@@ -9917,7 +9957,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>221</v>
       </c>
@@ -9931,7 +9971,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>241</v>
       </c>
@@ -9944,8 +9984,11 @@
       <c r="D19" s="3" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E19" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>241</v>
       </c>
@@ -9959,7 +10002,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>241</v>
       </c>
@@ -9973,7 +10016,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
         <v>241</v>
       </c>
@@ -9987,7 +10030,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
         <v>241</v>
       </c>
@@ -10001,7 +10044,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
         <v>241</v>
       </c>
@@ -10015,7 +10058,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>241</v>
       </c>
@@ -10029,7 +10072,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
         <v>241</v>
       </c>
@@ -10043,7 +10086,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
         <v>241</v>
       </c>
@@ -10057,7 +10100,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
         <v>241</v>
       </c>
@@ -10071,7 +10114,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
         <v>241</v>
       </c>
@@ -10085,7 +10128,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
         <v>241</v>
       </c>
@@ -10099,7 +10142,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
         <v>241</v>
       </c>
@@ -10113,7 +10156,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
         <v>241</v>
       </c>
@@ -12665,8 +12708,11 @@
       <c r="K16" s="12" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L16" s="19" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>416</v>
       </c>
@@ -12701,7 +12747,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>416</v>
       </c>
@@ -12736,7 +12782,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>416</v>
       </c>
@@ -12771,7 +12817,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="121.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="121.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>416</v>
       </c>
@@ -12806,7 +12852,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>416</v>
       </c>
@@ -12841,7 +12887,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>416</v>
       </c>
@@ -12876,7 +12922,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>524</v>
       </c>
@@ -12911,7 +12957,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>524</v>
       </c>
@@ -12945,8 +12991,11 @@
       <c r="K24" s="12" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L24" s="19" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>524</v>
       </c>
@@ -12981,7 +13030,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>524</v>
       </c>
@@ -13016,7 +13065,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>524</v>
       </c>
@@ -13050,8 +13099,11 @@
       <c r="K27" s="12" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L27" s="19" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>524</v>
       </c>
@@ -13085,8 +13137,11 @@
       <c r="K28" s="12" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L28" s="19" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>524</v>
       </c>
@@ -13121,7 +13176,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>524</v>
       </c>
@@ -13156,7 +13211,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>524</v>
       </c>
@@ -13191,7 +13246,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>524</v>
       </c>
@@ -13226,7 +13281,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="140" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>524</v>
       </c>
@@ -13260,8 +13315,11 @@
       <c r="K33" s="12" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L33" s="19" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>524</v>
       </c>
@@ -13296,7 +13354,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>524</v>
       </c>
@@ -13331,7 +13389,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>524</v>
       </c>
@@ -13366,7 +13424,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>524</v>
       </c>
@@ -13401,7 +13459,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>524</v>
       </c>
@@ -13436,7 +13494,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>524</v>
       </c>
@@ -13471,7 +13529,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
         <v>524</v>
       </c>
@@ -13506,7 +13564,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>524</v>
       </c>
@@ -13541,7 +13599,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>579</v>
       </c>
@@ -13576,7 +13634,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
         <v>579</v>
       </c>
@@ -13611,7 +13669,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>579</v>
       </c>
@@ -13646,7 +13704,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>579</v>
       </c>
@@ -13681,7 +13739,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>579</v>
       </c>
@@ -13716,7 +13774,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>579</v>
       </c>
@@ -13751,7 +13809,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>579</v>
       </c>
@@ -13786,7 +13844,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>579</v>
       </c>
@@ -13821,7 +13879,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>579</v>
       </c>
@@ -13856,7 +13914,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>579</v>
       </c>
@@ -13891,7 +13949,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>613</v>
       </c>
@@ -13922,7 +13980,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>613</v>
       </c>
@@ -13957,7 +14015,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>613</v>
       </c>
@@ -13992,7 +14050,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>613</v>
       </c>
@@ -14025,7 +14083,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
         <v>613</v>
       </c>
@@ -14056,7 +14114,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>613</v>
       </c>
@@ -14087,7 +14145,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="135" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="135" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>613</v>
       </c>
@@ -14120,7 +14178,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>613</v>
       </c>
@@ -14154,8 +14212,11 @@
       <c r="K59" s="12" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L59" s="19" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>613</v>
       </c>
@@ -14188,7 +14249,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>613</v>
       </c>
@@ -14223,7 +14284,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>613</v>
       </c>
@@ -14256,7 +14317,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>613</v>
       </c>
@@ -14291,7 +14352,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>613</v>
       </c>
@@ -29950,7 +30011,9 @@
       <c r="C2" s="6" t="s">
         <v>2447</v>
       </c>
-      <c r="D2" s="7"/>
+      <c r="D2" s="7" t="s">
+        <v>2517</v>
+      </c>
       <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" ht="297" customHeight="1" x14ac:dyDescent="0.2">
@@ -29961,6 +30024,9 @@
         <v>2449</v>
       </c>
       <c r="C3" s="16"/>
+      <c r="E3" t="s">
+        <v>2518</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="202.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
@@ -29968,6 +30034,9 @@
       </c>
       <c r="B4" s="17" t="s">
         <v>2451</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2519</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
